--- a/main/ig/StructureDefinition-fr-device-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-device-document.xlsx
+++ b/main/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2823,7 +2823,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>195</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>406</v>
       </c>
@@ -10313,7 +10313,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>426</v>
       </c>
@@ -10761,7 +10761,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>444</v>
       </c>
@@ -11779,7 +11779,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>473</v>
       </c>
@@ -14261,7 +14261,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
         <v>528</v>
       </c>
@@ -15053,12 +15053,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN114">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
